--- a/신입기수 교육세션 - RAG Agent 과제 명세서.xlsx
+++ b/신입기수 교육세션 - RAG Agent 과제 명세서.xlsx
@@ -1910,16 +1910,6 @@
     <mergeCell ref="C50:D50"/>
     <mergeCell ref="A3:H3"/>
   </mergeCells>
-  <conditionalFormatting sqref="A3:H50">
-    <cfRule type="colorScale" priority="1">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFFFFFFF"/>
-        <color rgb="FF57BB8A"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
   <hyperlinks>
     <hyperlink r:id="rId1" ref="C7"/>
   </hyperlinks>
